--- a/results/Int Task Remove ACC -0.8/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8105943050092904</v>
+        <v>0.807527800571574</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8020903011610688</v>
+        <v>0.8125518047970723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8056761268781303</v>
+        <v>0.8132297708987672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8056761268781303</v>
+        <v>0.8011125887779067</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.804833479528027</v>
+        <v>0.8011125887779067</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.802278373560454</v>
+        <v>0.7981832243947068</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8068419116606774</v>
+        <v>0.7985222074455542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8068419116606774</v>
+        <v>0.782701677937806</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8075551531271516</v>
+        <v>0.7900221650019336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8084506192052667</v>
+        <v>0.7907001311036285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8053899625552946</v>
+        <v>0.7867538175678862</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7922696018788375</v>
+        <v>0.7886956603755788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8017807456872565</v>
+        <v>0.7882351942503042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7859053224300387</v>
+        <v>0.8017748978995123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7852058515605105</v>
+        <v>0.7903041792818539</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7906237325863257</v>
+        <v>0.7910781622855418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7697046867189195</v>
+        <v>0.7657736528866379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7697046867189195</v>
+        <v>0.7739837582411364</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7697046867189195</v>
+        <v>0.7748537581468172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7588906180734369</v>
+        <v>0.7743580166567632</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7581813380115635</v>
+        <v>0.7655346481423841</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7373152995104836</v>
+        <v>0.7505997755204059</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6892913801722267</v>
+        <v>0.7498963432462767</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7244299821736793</v>
+        <v>0.7568680380672118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6974211256048215</v>
+        <v>0.7564683134791508</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6800369731096083</v>
+        <v>0.7564683134791508</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6290582232157174</v>
+        <v>0.7622408345359026</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.651591824415457</v>
+        <v>0.7660598172094735</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6278375446837008</v>
+        <v>0.7497141186346359</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5963179687426313</v>
+        <v>0.7497141186346359</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5990690699187912</v>
+        <v>0.7449330805579921</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5937413580072248</v>
+        <v>0.7477154956943305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5902809767691916</v>
+        <v>0.7390703903869915</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.592481442705828</v>
+        <v>0.7380690982145384</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5954304254737179</v>
+        <v>0.7253660054893749</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5954304254737179</v>
+        <v>0.7283404544296992</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5992395989549437</v>
+        <v>0.6953610065740452</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6033681371023268</v>
+        <v>0.6988272355998226</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5885488997670316</v>
+        <v>0.6815155202173113</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5901791120794545</v>
+        <v>0.6812274695113325</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5765532007205983</v>
+        <v>0.6809492279976986</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5750855946351263</v>
+        <v>0.646605925129453</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5314018656329287</v>
+        <v>0.6428574931854409</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5443283061222565</v>
+        <v>0.6433023023306264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5494992595946162</v>
+        <v>0.6416073870763891</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5306180734368957</v>
+        <v>0.6260611376776737</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5386929251200211</v>
+        <v>0.6195949935391377</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5386929251200211</v>
+        <v>0.616887090536959</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5419103402091998</v>
+        <v>0.6677700121671712</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5098714429887855</v>
+        <v>0.6615272157927997</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5111666336549616</v>
+        <v>0.6362817501862803</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.511105892117748</v>
+        <v>0.6065197174198051</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5007756807485169</v>
+        <v>0.5763089141035436</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5005247917904605</v>
+        <v>0.6011546551220018</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5122401743018025</v>
+        <v>0.5994597398677646</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5360787753600633</v>
+        <v>0.6019169425502013</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5391298114560048</v>
+        <v>0.5884281712458618</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5642752987559303</v>
+        <v>0.5660688718485611</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5799330333984136</v>
+        <v>0.562449845788178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5524303217226451</v>
+        <v>0.5433864350188167</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5527693047734925</v>
+        <v>0.5251869877290777</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5812714222385709</v>
+        <v>0.5000630051969855</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6150461692274318</v>
+        <v>0.5071031757260217</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6103004065155674</v>
+        <v>0.5071031757260217</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6103004065155674</v>
+        <v>0.5073363326825311</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6109783726172623</v>
+        <v>0.4963321166162059</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5597323222319686</v>
+        <v>0.5012561425351103</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5772419192062099</v>
+        <v>0.5012561425351103</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5800537619195835</v>
+        <v>0.5012561425351103</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5579491242466257</v>
+        <v>0.4988930703715232</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5413095271780651</v>
+        <v>0.4926640445940975</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4733382379295059</v>
+        <v>0.5048791300000943</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4937162691114192</v>
+        <v>0.4934497231732737</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5039523499618008</v>
+        <v>0.491309998773851</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5013012270922347</v>
+        <v>0.4906516510568462</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5039680069418899</v>
+        <v>0.5135928996538487</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5022476255152184</v>
+        <v>0.5038880242966148</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5018537487149015</v>
+        <v>0.5032570291351877</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.505445422219707</v>
+        <v>0.5032570291351877</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5123974986559521</v>
+        <v>0.5071778764984956</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5347411410731634</v>
+        <v>0.4966909066900578</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5205547852824387</v>
+        <v>0.4864272846457844</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5275344029125756</v>
+        <v>0.5097624100431039</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5289256104807447</v>
+        <v>0.4919215641889024</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5366065853635532</v>
+        <v>0.4969495298190015</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5227748696037653</v>
+        <v>0.5049655263480566</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5052101902417401</v>
+        <v>0.5080397649566604</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5036014826971507</v>
+        <v>0.5080397649566604</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4975859954915443</v>
+        <v>0.4943863124039124</v>
       </c>
     </row>
   </sheetData>
